--- a/GenAI Learning Roadmap.xlsx
+++ b/GenAI Learning Roadmap.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\267564\OneDrive - NTT Data Group\ValueX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\267564\OneDrive - NTT Data Group\ValueX\GitRepos\Documents\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C5DC77E-DE6E-4006-BD38-C6583B72C5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED7E9C3-A21C-439C-8668-9356F0657424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19065" yWindow="0" windowWidth="19440" windowHeight="10320" xr2:uid="{1684B1F0-1F6A-4729-96C5-DDAA8F3EA7A9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1684B1F0-1F6A-4729-96C5-DDAA8F3EA7A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
   <si>
     <t>Topics</t>
   </si>
@@ -138,13 +138,109 @@
   </si>
   <si>
     <t>Reading</t>
+  </si>
+  <si>
+    <t>Langchain</t>
+  </si>
+  <si>
+    <t>Lang Graph</t>
+  </si>
+  <si>
+    <t>Lanchain Agents</t>
+  </si>
+  <si>
+    <t>Langchain documentation and information</t>
+  </si>
+  <si>
+    <t>https://python.langchain.com/v0.1/docs/modules/agents/</t>
+  </si>
+  <si>
+    <t>Read documentation and how to guides</t>
+  </si>
+  <si>
+    <t>Langchain Agents</t>
+  </si>
+  <si>
+    <t>Implementing Agents with Lanchain</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ziu87EXZVUE</t>
+  </si>
+  <si>
+    <t>Sam Witteveen</t>
+  </si>
+  <si>
+    <t>Watch video and follow notebook</t>
+  </si>
+  <si>
+    <t>Video and notebook exercise</t>
+  </si>
+  <si>
+    <t>Agentic AI Systems</t>
+  </si>
+  <si>
+    <t>https://www.deeplearning.ai/short-courses/multi-ai-agent-systems-with-crewai/</t>
+  </si>
+  <si>
+    <t>Deeplearning AI</t>
+  </si>
+  <si>
+    <t>Hands on exercise to implement Muti Agent Systems</t>
+  </si>
+  <si>
+    <t>Exercise</t>
+  </si>
+  <si>
+    <t>MCP</t>
+  </si>
+  <si>
+    <t>n8n/crew.ai</t>
+  </si>
+  <si>
+    <t>DevOps</t>
+  </si>
+  <si>
+    <t>Azure AI Studio</t>
+  </si>
+  <si>
+    <t>Intro to AI studio</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fQ9RFR1KTbY</t>
+  </si>
+  <si>
+    <t>Watch video</t>
+  </si>
+  <si>
+    <t>Hands on in AI studio</t>
+  </si>
+  <si>
+    <t>Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">using the Azure AI Studio, create a chatbot and also a knowledge base to query the chatbot over </t>
+  </si>
+  <si>
+    <t>Amazon Bedrock</t>
+  </si>
+  <si>
+    <t>Hands on with Bedrock</t>
+  </si>
+  <si>
+    <t>https://catalog.us-east-1.prod.workshops.aws/workshops/a4bdb007-5600-4368-81c5-ff5b4154f518/en-US</t>
+  </si>
+  <si>
+    <t>Aws</t>
+  </si>
+  <si>
+    <t>Complete the training to understand fundamental GenAI implementatinos using bedrock</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,13 +263,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -204,7 +320,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -212,11 +328,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -553,92 +671,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE8C1DE-6E51-488E-BC4C-B995D6F4B664}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="5.42578125" customWidth="1"/>
     <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
-    <col min="4" max="4" width="64" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -647,31 +769,36 @@
       <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="C5" s="1"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -689,32 +816,272 @@
       <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{4695513A-E8F4-4888-888F-31686C8E9D5F}"/>
-    <hyperlink ref="D6" r:id="rId2" xr:uid="{A11D6FA8-9572-4C47-8398-96A889BB2E59}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{DE7C3A35-CA96-4871-8987-2FB228113558}"/>
+    <hyperlink ref="D6" r:id="rId2" xr:uid="{2E67737B-B2ED-4166-96F8-603FED4E569E}"/>
+    <hyperlink ref="D13" r:id="rId3" xr:uid="{FEBBBC1D-1339-49A3-B234-A52314FCF19A}"/>
+    <hyperlink ref="E13" r:id="rId4" display="https://www.youtube.com/@samwitteveenai" xr:uid="{BD1030F5-4D0C-444F-9DFA-7514118FD6B2}"/>
+    <hyperlink ref="D12" r:id="rId5" xr:uid="{7ABA2D64-DEC2-407E-BDC1-3E6D1664D307}"/>
+    <hyperlink ref="D14" r:id="rId6" xr:uid="{9975E14A-E0E0-45FA-894A-4ABE81A32C12}"/>
+    <hyperlink ref="E18" r:id="rId7" display="https://www.youtube.com/@samwitteveenai" xr:uid="{A2C02E57-EC9D-4192-85BC-6F788953B21B}"/>
+    <hyperlink ref="D20" r:id="rId8" xr:uid="{3D44D625-C2FB-4D57-9548-31F87BD2405A}"/>
+    <hyperlink ref="D18" r:id="rId9" xr:uid="{3DA61AAD-4B06-4A57-BAF7-9B6B4D5F03DD}"/>
+    <hyperlink ref="D3" r:id="rId10" location="content" xr:uid="{E51736A3-B398-4941-B7A8-A3D757531B4F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GenAI Learning Roadmap.xlsx
+++ b/GenAI Learning Roadmap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\267564\OneDrive - NTT Data Group\ValueX\GitRepos\Documents\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED7E9C3-A21C-439C-8668-9356F0657424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F281883C-1BD1-4945-9432-90F167A1DBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1684B1F0-1F6A-4729-96C5-DDAA8F3EA7A9}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{1684B1F0-1F6A-4729-96C5-DDAA8F3EA7A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="71">
   <si>
     <t>Topics</t>
   </si>
@@ -234,13 +234,31 @@
   </si>
   <si>
     <t>Complete the training to understand fundamental GenAI implementatinos using bedrock</t>
+  </si>
+  <si>
+    <t>https://cloud.google.com/use-cases/retrieval-augmented-generation</t>
+  </si>
+  <si>
+    <t>What are Embeddings and how do it work?</t>
+  </si>
+  <si>
+    <t>https://medium.com/@eugenesh4work/what-are-embeddings-and-how-do-it-work-b35af573b59e</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/data-engineering/playbook/solutions/vector-database/</t>
+  </si>
+  <si>
+    <t>Lanchain intro and basics</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=J_0qvRt4LNk</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,12 +287,6 @@
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -320,7 +332,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -330,9 +342,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -818,7 +827,7 @@
       </c>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -826,27 +835,33 @@
         <v>23</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="D7" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -854,21 +869,27 @@
         <v>25</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -907,7 +928,7 @@
       <c r="F12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H12" s="4"/>
@@ -925,13 +946,13 @@
       <c r="D13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="1" t="s">
         <v>44</v>
       </c>
       <c r="H13" s="4"/>
@@ -1013,7 +1034,7 @@
       <c r="D18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -1072,16 +1093,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{DE7C3A35-CA96-4871-8987-2FB228113558}"/>
-    <hyperlink ref="D6" r:id="rId2" xr:uid="{2E67737B-B2ED-4166-96F8-603FED4E569E}"/>
-    <hyperlink ref="D13" r:id="rId3" xr:uid="{FEBBBC1D-1339-49A3-B234-A52314FCF19A}"/>
-    <hyperlink ref="E13" r:id="rId4" display="https://www.youtube.com/@samwitteveenai" xr:uid="{BD1030F5-4D0C-444F-9DFA-7514118FD6B2}"/>
-    <hyperlink ref="D12" r:id="rId5" xr:uid="{7ABA2D64-DEC2-407E-BDC1-3E6D1664D307}"/>
-    <hyperlink ref="D14" r:id="rId6" xr:uid="{9975E14A-E0E0-45FA-894A-4ABE81A32C12}"/>
-    <hyperlink ref="E18" r:id="rId7" display="https://www.youtube.com/@samwitteveenai" xr:uid="{A2C02E57-EC9D-4192-85BC-6F788953B21B}"/>
-    <hyperlink ref="D20" r:id="rId8" xr:uid="{3D44D625-C2FB-4D57-9548-31F87BD2405A}"/>
-    <hyperlink ref="D18" r:id="rId9" xr:uid="{3DA61AAD-4B06-4A57-BAF7-9B6B4D5F03DD}"/>
-    <hyperlink ref="D3" r:id="rId10" location="content" xr:uid="{E51736A3-B398-4941-B7A8-A3D757531B4F}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{376998E4-6FED-40F1-B6B3-361DF31D9A54}"/>
+    <hyperlink ref="D6" r:id="rId2" xr:uid="{251DCB06-1FBB-46E7-81BD-F14E2657218C}"/>
+    <hyperlink ref="D13" r:id="rId3" xr:uid="{635097EE-C272-4778-A3DC-C646A9C129D9}"/>
+    <hyperlink ref="E13" r:id="rId4" display="https://www.youtube.com/@samwitteveenai" xr:uid="{C23EC549-9885-4B4B-9050-E52F6593E736}"/>
+    <hyperlink ref="D12" r:id="rId5" xr:uid="{44F28B66-F120-4804-8609-160870514B23}"/>
+    <hyperlink ref="D14" r:id="rId6" xr:uid="{8A30DA20-1194-4C43-BEB6-139EA8529854}"/>
+    <hyperlink ref="E18" r:id="rId7" display="https://www.youtube.com/@samwitteveenai" xr:uid="{5BF7098E-FAFF-4B9F-A50B-75776947291D}"/>
+    <hyperlink ref="D20" r:id="rId8" xr:uid="{EB0A5EFC-D098-4FDB-B087-FC01DAE2C46F}"/>
+    <hyperlink ref="D18" r:id="rId9" xr:uid="{9960C19D-C231-4D34-8B44-D7146DECE135}"/>
+    <hyperlink ref="D3" r:id="rId10" location="content" xr:uid="{6D5B8E86-4787-4C09-9AA0-1DEE45EA8B23}"/>
+    <hyperlink ref="D9" r:id="rId11" xr:uid="{8E07A8FE-C1FA-49E0-90C8-798BCC90D506}"/>
+    <hyperlink ref="D8" r:id="rId12" xr:uid="{19322042-DAF9-4C31-BD0E-7EBC7D498900}"/>
+    <hyperlink ref="D7" r:id="rId13" xr:uid="{9A7B78B0-998A-4606-AA75-473867956BB5}"/>
+    <hyperlink ref="D10" r:id="rId14" xr:uid="{CF897636-27B6-49B7-9DE5-F7DAC4C565D7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
